--- a/AppData/c82f97b5-b4de-4395-adb4-1452737f83dc/ADM/t012.xlsx
+++ b/AppData/c82f97b5-b4de-4395-adb4-1452737f83dc/ADM/t012.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\Other\Defaults\AppData\c82f97b5-b4de-4395-adb4-1452737f83dc\ADM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{066477E7-4038-4B5E-870F-88B8AE648C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40652231-1503-4FDD-AB68-08341E0E8916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="1620" windowWidth="25950" windowHeight="16695" xr2:uid="{6F2B46CF-07BD-4EE8-AADA-1AF6502570B4}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25950" windowHeight="16695" xr2:uid="{6F2B46CF-07BD-4EE8-AADA-1AF6502570B4}"/>
   </bookViews>
   <sheets>
     <sheet name="T012" sheetId="1" r:id="rId1"/>
@@ -27,18 +27,14 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0000-0000-0000-000000000000}" name="Connection1" type="4" refreshedVersion="3" deleted="1" background="1" saveData="1">
-    <webPr sourceData="1" parsePre="1" consecutive="1" xl2000="1" htmlTables="1">
-      <tables count="1">
-        <s v="cap oli1"/>
-      </tables>
-    </webPr>
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Connection1" type="4" refreshedVersion="3" deleted="1" background="1" saveData="1">
+    <webPr sourceData="1" parsePre="1" consecutive="1" xl2000="1" htmlTables="1"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="77">
   <si>
     <t>T012 - Tabella codici prodotto accisa</t>
   </si>
@@ -269,58 +265,13 @@
   </si>
   <si>
     <t>Additivi di cui ai codici NC 3811 11, 3811 19 00 e 3811 90 00</t>
-  </si>
-  <si>
-    <t>Legenda delle colonne:</t>
-  </si>
-  <si>
-    <t>CPA:</t>
-  </si>
-  <si>
-    <t>Codice prodotto accise</t>
-  </si>
-  <si>
-    <t>CAT.:</t>
-  </si>
-  <si>
-    <t>Categoria di prodotto accise T=Tabacchi, B=Birra, W=Vino, I=Prodotti alcolici intermedi,</t>
-  </si>
-  <si>
-    <t>S=Alcool etilico, E=Prodotti energetici</t>
-  </si>
-  <si>
-    <t>U.M.:</t>
-  </si>
-  <si>
-    <t>unità di misura (secondo la T013)</t>
-  </si>
-  <si>
-    <t>A:</t>
-  </si>
-  <si>
-    <t>deve essere fornito il grado alcolico (S=SI N=NO) eccetto per B000 (Birra) se è fornito</t>
-  </si>
-  <si>
-    <t>il grado Plato</t>
-  </si>
-  <si>
-    <t>P:</t>
-  </si>
-  <si>
-    <t>deve essere fornito il grado Plato (S=SI N=NO)</t>
-  </si>
-  <si>
-    <t>D:</t>
-  </si>
-  <si>
-    <t>deve essere fornita la densità a 15°C (S=SI N=NO)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -336,13 +287,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -575,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -633,12 +577,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -981,8 +919,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BFBE623-0991-4463-9742-D81F7DD83474}">
-  <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="13.15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -994,15 +932,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
@@ -1739,73 +1677,6 @@
       </c>
       <c r="G34" s="19" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B37" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B38" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B39" s="20"/>
-      <c r="C39" s="21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B40" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B41" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E41" s="21"/>
-    </row>
-    <row r="42" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B42" s="20"/>
-      <c r="C42" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E42" s="21"/>
-    </row>
-    <row r="43" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B43" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B44" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
